--- a/data/C.xlsx
+++ b/data/C.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\CC_scripts\Shermo_post\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lrc\Desktop\ThermoCR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D34709-0848-44FB-9E82-4F478E7E1C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A6C7E6-C8F8-4714-8CA7-CC316C846ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -302,7 +291,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>T(K)</t>
+    <t>T/K</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -681,9 +670,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N65"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="34.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="33" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -715,7 +704,7 @@
       <c r="L1" s="2"/>
       <c r="N1" s="2"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -744,7 +733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>100</v>
       </c>
@@ -774,7 +763,7 @@
         <v>134.23000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>200</v>
       </c>
@@ -804,7 +793,7 @@
         <v>146.68499999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>250</v>
       </c>
@@ -834,7 +823,7 @@
         <v>150.0319999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>300</v>
       </c>
@@ -864,7 +853,7 @@
         <v>152.43666666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>350</v>
       </c>
@@ -894,7 +883,7 @@
         <v>154.19714285714301</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>400</v>
       </c>
@@ -924,7 +913,7 @@
         <v>155.505</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>450</v>
       </c>
@@ -954,7 +943,7 @@
         <v>156.47999999999988</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>500</v>
       </c>
@@ -984,7 +973,7 @@
         <v>157.202</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>600</v>
       </c>
@@ -1014,7 +1003,7 @@
         <v>158.12333333333339</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>700</v>
       </c>
@@ -1044,7 +1033,7 @@
         <v>158.59857142857143</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>800</v>
       </c>
@@ -1074,7 +1063,7 @@
         <v>158.81250000000009</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>900</v>
       </c>
@@ -1104,7 +1093,7 @@
         <v>158.8666666666667</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>1000</v>
       </c>
@@ -1134,7 +1123,7 @@
         <v>158.82100000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>1100</v>
       </c>
@@ -1164,7 +1153,7 @@
         <v>158.71181818181816</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>1200</v>
       </c>
@@ -1194,7 +1183,7 @@
         <v>158.56249999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1300</v>
       </c>
@@ -1224,7 +1213,7 @@
         <v>158.3861538461538</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1400</v>
       </c>
@@ -1254,7 +1243,7 @@
         <v>158.19428571428566</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1500</v>
       </c>
@@ -1284,7 +1273,7 @@
         <v>157.99199999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>1600</v>
       </c>
@@ -1314,7 +1303,7 @@
         <v>157.78312499999998</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>1700</v>
       </c>
@@ -1344,7 +1333,7 @@
         <v>157.57235294117652</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>1800</v>
       </c>
@@ -1374,7 +1363,7 @@
         <v>157.36055555555555</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>1900</v>
       </c>
@@ -1404,7 +1393,7 @@
         <v>157.15000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>2000</v>
       </c>
@@ -1434,7 +1423,7 @@
         <v>156.94149999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>2100</v>
       </c>
@@ -1464,7 +1453,7 @@
         <v>156.73619047619044</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>2200</v>
       </c>
@@ -1494,7 +1483,7 @@
         <v>156.53409090909091</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>2300</v>
       </c>
@@ -1524,7 +1513,7 @@
         <v>156.33652173913046</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>2400</v>
       </c>
@@ -1554,7 +1543,7 @@
         <v>156.14250000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>2500</v>
       </c>
@@ -1584,7 +1573,7 @@
         <v>155.95320000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>2600</v>
       </c>
@@ -1614,7 +1603,7 @@
         <v>155.76769230769233</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>2700</v>
       </c>
@@ -1644,7 +1633,7 @@
         <v>155.58666666666664</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>2800</v>
       </c>
@@ -1674,7 +1663,7 @@
         <v>155.41035714285712</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>2900</v>
       </c>
@@ -1704,7 +1693,7 @@
         <v>155.23793103448276</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>3000</v>
       </c>
@@ -1734,7 +1723,7 @@
         <v>155.06966666666668</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>3100</v>
       </c>
@@ -1764,7 +1753,7 @@
         <v>154.90548387096777</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>3200</v>
       </c>
@@ -1794,7 +1783,7 @@
         <v>154.7446875</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>3300</v>
       </c>
@@ -1824,7 +1813,7 @@
         <v>154.58757575757576</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>3400</v>
       </c>
@@ -1854,7 +1843,7 @@
         <v>154.43382352941177</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>3500</v>
       </c>
@@ -1884,7 +1873,7 @@
         <v>154.28314285714285</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>3600</v>
       </c>
@@ -1914,7 +1903,7 @@
         <v>154.13583333333332</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>3700</v>
       </c>
@@ -1944,7 +1933,7 @@
         <v>153.99135135135131</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>3800</v>
       </c>
@@ -1974,7 +1963,7 @@
         <v>153.84947368421052</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>3900</v>
       </c>
@@ -2004,7 +1993,7 @@
         <v>153.71</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>4000</v>
       </c>
@@ -2034,7 +2023,7 @@
         <v>153.57300000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>4100</v>
       </c>
@@ -2064,7 +2053,7 @@
         <v>153.4380487804878</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>4200</v>
       </c>
@@ -2094,7 +2083,7 @@
         <v>153.30500000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>4300</v>
       </c>
@@ -2124,7 +2113,7 @@
         <v>153.17418604651166</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>4400</v>
       </c>
@@ -2154,7 +2143,7 @@
         <v>153.04499999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>4500</v>
       </c>
@@ -2184,7 +2173,7 @@
         <v>152.91755555555557</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>4600</v>
       </c>
@@ -2214,7 +2203,7 @@
         <v>152.79173913043482</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>4700</v>
       </c>
@@ -2244,7 +2233,7 @@
         <v>152.66723404255319</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>4800</v>
       </c>
@@ -2274,7 +2263,7 @@
         <v>152.54395833333334</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>4900</v>
       </c>
@@ -2304,7 +2293,7 @@
         <v>152.4220408163265</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>5000</v>
       </c>
@@ -2334,7 +2323,7 @@
         <v>152.30119999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>5100</v>
       </c>
@@ -2364,7 +2353,7 @@
         <v>152.18137254901961</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>5200</v>
       </c>
@@ -2394,7 +2383,7 @@
         <v>152.06269230769232</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>5300</v>
       </c>
@@ -2424,7 +2413,7 @@
         <v>151.94471698113207</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>5400</v>
       </c>
@@ -2454,7 +2443,7 @@
         <v>151.82777777777778</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>5500</v>
       </c>
@@ -2484,7 +2473,7 @@
         <v>151.71145454545456</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>5600</v>
       </c>
@@ -2514,7 +2503,7 @@
         <v>151.59589285714284</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>5700</v>
       </c>
@@ -2544,7 +2533,7 @@
         <v>151.48122807017543</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>5800</v>
       </c>
@@ -2574,7 +2563,7 @@
         <v>151.36706896551723</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>5900</v>
       </c>
@@ -2604,7 +2593,7 @@
         <v>151.25355932203391</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>6000</v>
       </c>
